--- a/docs/downloads/11/tbl_degats_stocks_riz_marovoay_tous.xlsx
+++ b/docs/downloads/11/tbl_degats_stocks_riz_marovoay_tous.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E32"/>
+  <dimension ref="A1:E27"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -389,7 +389,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Autres bestioles</t>
+          <t>Maladie</t>
         </is>
       </c>
       <c r="C2">
@@ -410,14 +410,14 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Maladie</t>
+          <t>Rats</t>
         </is>
       </c>
       <c r="C3">
-        <v>100</v>
+        <v>83.3</v>
       </c>
       <c r="D3">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="E3">
         <v>0</v>
@@ -431,38 +431,38 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Rats</t>
+          <t>Sécheresse</t>
         </is>
       </c>
       <c r="C4">
-        <v>83.3</v>
+        <v>90.2</v>
       </c>
       <c r="D4">
-        <v>16.7</v>
+        <v>4.9</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>4.9</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Marovoay - Bepako</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Sécheresse</t>
+          <t>Maladie</t>
         </is>
       </c>
       <c r="C5">
-        <v>90.2</v>
+        <v>100</v>
       </c>
       <c r="D5">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>4.9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -473,17 +473,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Autres bestioles</t>
+          <t>Rats</t>
         </is>
       </c>
       <c r="C6">
-        <v>66.7</v>
+        <v>30</v>
       </c>
       <c r="D6">
-        <v>33.3</v>
+        <v>60</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7">
@@ -494,14 +494,14 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Facteur humain</t>
+          <t>Sécheresse</t>
         </is>
       </c>
       <c r="C7">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="D7">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="E7">
         <v>0</v>
@@ -510,12 +510,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Marovoay - Madiromiongana</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Maladie</t>
+          <t>Autres bestioles</t>
         </is>
       </c>
       <c r="C8">
@@ -531,40 +531,40 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Marovoay - Madiromiongana</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Rats</t>
+          <t>Criquets</t>
         </is>
       </c>
       <c r="C9">
-        <v>30</v>
+        <v>100</v>
       </c>
       <c r="D9">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="E9">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Marovoay - Madiromiongana</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Sécheresse</t>
+          <t>Cyclone</t>
         </is>
       </c>
       <c r="C10">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="D10">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E10">
         <v>0</v>
@@ -578,7 +578,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Autres bestioles</t>
+          <t>Facteur humain</t>
         </is>
       </c>
       <c r="C11">
@@ -599,14 +599,14 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Criquets</t>
+          <t>Inondation</t>
         </is>
       </c>
       <c r="C12">
-        <v>100</v>
+        <v>85.7</v>
       </c>
       <c r="D12">
-        <v>0</v>
+        <v>14.3</v>
       </c>
       <c r="E12">
         <v>0</v>
@@ -620,7 +620,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Cyclone</t>
+          <t>Maladie</t>
         </is>
       </c>
       <c r="C13">
@@ -641,17 +641,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Facteur humain</t>
+          <t>Rats</t>
         </is>
       </c>
       <c r="C14">
-        <v>100</v>
+        <v>31.6</v>
       </c>
       <c r="D14">
-        <v>0</v>
+        <v>63.2</v>
       </c>
       <c r="E14">
-        <v>0</v>
+        <v>5.3</v>
       </c>
     </row>
     <row r="15">
@@ -662,28 +662,28 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Inondation</t>
+          <t>Sécheresse</t>
         </is>
       </c>
       <c r="C15">
-        <v>85.7</v>
+        <v>91</v>
       </c>
       <c r="D15">
-        <v>14.3</v>
+        <v>3.4</v>
       </c>
       <c r="E15">
-        <v>0</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Marovoay - Maroala</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Maladie</t>
+          <t>Autres</t>
         </is>
       </c>
       <c r="C16">
@@ -699,28 +699,28 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Marovoay - Maroala</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Rats</t>
+          <t>Maladie</t>
         </is>
       </c>
       <c r="C17">
-        <v>31.6</v>
+        <v>100</v>
       </c>
       <c r="D17">
-        <v>63.2</v>
+        <v>0</v>
       </c>
       <c r="E17">
-        <v>5.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Marovoay - Maroala</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -729,19 +729,19 @@
         </is>
       </c>
       <c r="C18">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="D18">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="E18">
-        <v>5.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Marovoay - Tous</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -762,19 +762,19 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Marovoay - Tous</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Criquets</t>
+          <t>Autres bestioles</t>
         </is>
       </c>
       <c r="C20">
-        <v>100</v>
+        <v>92.3</v>
       </c>
       <c r="D20">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="E20">
         <v>0</v>
@@ -783,12 +783,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Marovoay - Tous</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Facteur humain</t>
+          <t>Criquets</t>
         </is>
       </c>
       <c r="C21">
@@ -804,12 +804,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Marovoay - Tous</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Maladie</t>
+          <t>Cyclone</t>
         </is>
       </c>
       <c r="C22">
@@ -825,12 +825,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Marovoay - Tous</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Sécheresse</t>
+          <t>Facteur humain</t>
         </is>
       </c>
       <c r="C23">
@@ -851,14 +851,14 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Autres</t>
+          <t>Inondation</t>
         </is>
       </c>
       <c r="C24">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="D24">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="E24">
         <v>0</v>
@@ -872,14 +872,14 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Autres bestioles</t>
+          <t>Maladie</t>
         </is>
       </c>
       <c r="C25">
-        <v>92.3</v>
+        <v>100</v>
       </c>
       <c r="D25">
-        <v>7.7</v>
+        <v>0</v>
       </c>
       <c r="E25">
         <v>0</v>
@@ -893,17 +893,17 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Criquets</t>
+          <t>Rats</t>
         </is>
       </c>
       <c r="C26">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="D26">
-        <v>0</v>
+        <v>54.3</v>
       </c>
       <c r="E26">
-        <v>0</v>
+        <v>5.7</v>
       </c>
     </row>
     <row r="27">
@@ -914,121 +914,16 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Cyclone</t>
+          <t>Sécheresse</t>
         </is>
       </c>
       <c r="C27">
-        <v>100</v>
+        <v>93.3</v>
       </c>
       <c r="D27">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="E27">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Marovoay - Tous</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Facteur humain</t>
-        </is>
-      </c>
-      <c r="C28">
-        <v>100</v>
-      </c>
-      <c r="D28">
-        <v>0</v>
-      </c>
-      <c r="E28">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Marovoay - Tous</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Inondation</t>
-        </is>
-      </c>
-      <c r="C29">
-        <v>90</v>
-      </c>
-      <c r="D29">
-        <v>10</v>
-      </c>
-      <c r="E29">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Marovoay - Tous</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Maladie</t>
-        </is>
-      </c>
-      <c r="C30">
-        <v>100</v>
-      </c>
-      <c r="D30">
-        <v>0</v>
-      </c>
-      <c r="E30">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Marovoay - Tous</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Rats</t>
-        </is>
-      </c>
-      <c r="C31">
-        <v>40</v>
-      </c>
-      <c r="D31">
-        <v>54.3</v>
-      </c>
-      <c r="E31">
-        <v>5.7</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Marovoay - Tous</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Sécheresse</t>
-        </is>
-      </c>
-      <c r="C32">
-        <v>93.3</v>
-      </c>
-      <c r="D32">
-        <v>3.6</v>
-      </c>
-      <c r="E32">
         <v>3.1</v>
       </c>
     </row>

--- a/docs/downloads/11/tbl_degats_stocks_riz_marovoay_tous.xlsx
+++ b/docs/downloads/11/tbl_degats_stocks_riz_marovoay_tous.xlsx
@@ -384,7 +384,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Ampijoroa</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -405,7 +405,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Ampijoroa</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -426,7 +426,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Ampijoroa</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -447,7 +447,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -468,7 +468,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -489,7 +489,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -510,7 +510,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -531,7 +531,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -552,7 +552,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -573,7 +573,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -594,7 +594,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -615,7 +615,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -636,7 +636,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -657,7 +657,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -678,7 +678,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -699,7 +699,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -720,7 +720,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -741,7 +741,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -762,7 +762,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -783,7 +783,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -804,7 +804,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -825,7 +825,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -846,7 +846,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -867,7 +867,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -888,7 +888,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -909,7 +909,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
